--- a/Metrics/Break-Even Graphs.xlsx
+++ b/Metrics/Break-Even Graphs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Metrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="13_ncr:1_{9B12405A-E811-4AF6-99FE-4D99CF93FFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8853E508-F918-43D6-9C6C-1725FFB7DDEC}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{9B12405A-E811-4AF6-99FE-4D99CF93FFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79AD2E7D-AB47-49FF-85BA-B57A47463183}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" tabRatio="846" xr2:uid="{72DB8043-9B22-441A-BCD0-4EB4CA42FDB6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
   <si>
     <t>NMAP</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Human (hrs)</t>
+  </si>
+  <si>
+    <t>AVG</t>
   </si>
 </sst>
 </file>
@@ -450,7 +453,177 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Break-even</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{0E0DF3F7-3A9D-42F3-B08F-A40F7B4F7C61}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-NZ"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.16289705265853602"/>
+                      <c:h val="0.11560185185185186"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-1614-4165-AE8E-B6EC13F6CFD0}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.3190570950991809</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>31.531042403442218</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'Break-Even'!$F$9</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="1"/>
+                  <c:pt idx="0">
+                    <c:v>3.32 reports, 31.5 hours</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1614-4165-AE8E-B6EC13F6CFD0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -465,6 +638,7 @@
         <c:axId val="2024312128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="8"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1087,6 +1261,174 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Break-even</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{1FE53C99-B849-418E-9327-E5251F3F95DD}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-NZ"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.17400154897000947"/>
+                      <c:h val="0.11560185185185186"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-0AD2-4B7D-90E3-AE121DC9B189}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$D$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.7081873415278492</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$E$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>19.09716480886842</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'Break-Even'!$F$23</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="1"/>
+                  <c:pt idx="0">
+                    <c:v>3.71 reports, 19.1 hours</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0AD2-4B7D-90E3-AE121DC9B189}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -1102,6 +1444,7 @@
         <c:axId val="638347519"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="8"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1502,7 +1845,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-NZ"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1746,6 +2089,174 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Break-even</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{47678D1A-A56E-459D-9807-7DF85CC73FFD}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-NZ"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.19070569767113038"/>
+                      <c:h val="0.11560185185185186"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-4360-47CD-9996-0EA93FF6DE21}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$D$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.298424938414984</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$E$37</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>13.049170631070588</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'Break-Even'!$F$37</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="1"/>
+                  <c:pt idx="0">
+                    <c:v>1.30 reports, 13.0 hours</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4360-47CD-9996-0EA93FF6DE21}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -1761,6 +2272,7 @@
         <c:axId val="509188287"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="8"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2088,6 +2600,819 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-NZ"/>
+              <a:t>Average Break-even chart</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Break-Even'!$B$50</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Human (hrs)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$A$51:$A$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$B$51:$B$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.2333333333333325</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16.466666666666665</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32.93333333333333</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>41.166666666666664</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>49.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>57.633333333333333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>65.86666666666666</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>74.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>82.333333333333329</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3263-4267-AF9B-9BB3297AABEC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Break-Even'!$C$50</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AI+setup (hrs)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$A$51:$A$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$C$51:$C$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>21.166666666666668</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.191141666666667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.215616666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.240091666666668</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21.264566666666667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21.289041666666666</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.313516666666668</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21.337991666666667</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21.362466666666666</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>21.386941666666669</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21.411416666666668</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3263-4267-AF9B-9BB3297AABEC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Break-even</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{8827ABCC-F48D-474F-AB6D-2AD968155E3F}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-NZ"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.16993626166333234"/>
+                      <c:h val="0.11560185185185186"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-3263-4267-AF9B-9BB3297AABEC}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$D$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.5785152827788682</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Break-Even'!$E$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>21.229775828212681</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'Break-Even'!$F$51</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="1"/>
+                  <c:pt idx="0">
+                    <c:v>2.58 reports, 21.2 hours</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3263-4267-AF9B-9BB3297AABEC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="197157312"/>
+        <c:axId val="1519122368"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="197157312"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="8"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-NZ" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Reports Produced</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1519122368"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1519122368"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-NZ"/>
+                  <a:t>Hours taken</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="197157312"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2208,6 +3533,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3756,20 +5121,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>275587</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>397113</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>101590</xdr:rowOff>
+      <xdr:rowOff>70513</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>578188</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>92892</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>177790</xdr:rowOff>
+      <xdr:rowOff>146713</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3796,16 +5677,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>388454</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>22018</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>85118</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
+      <xdr:rowOff>98218</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3832,16 +5713,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>233362</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>427653</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
+      <xdr:rowOff>152488</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>538162</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>124317</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>38188</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3866,7 +5747,47 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>392206</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>12326</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>123264</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>88526</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8ABEE62-53BD-39AF-15F5-AFEF28BCF75B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4186,7 +6107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{275EBB12-0F36-4113-9F1A-DF69764B9290}">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
@@ -4195,7 +6116,7 @@
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
@@ -4205,8 +6126,11 @@
       <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -4219,8 +6143,12 @@
       <c r="D2">
         <v>36180</v>
       </c>
+      <c r="E2">
+        <f>AVERAGE(B2,C2,D2)</f>
+        <v>29640</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -4233,8 +6161,12 @@
       <c r="D3">
         <v>136.33000000000001</v>
       </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E5" si="0">AVERAGE(B3,C3,D3)</f>
+        <v>88.110000000000014</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -4247,8 +6179,12 @@
       <c r="D4">
         <v>46800</v>
       </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>76200</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -4257,20 +6193,24 @@
         <v>3.3190570950991809</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:D5" si="0">C4/(C2-C3)</f>
+        <f t="shared" ref="C5:E5" si="1">C4/(C2-C3)</f>
         <v>3.7081873415278492</v>
       </c>
       <c r="D5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.298424938414984</v>
       </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>2.5785152827788682</v>
+      </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -4280,8 +6220,11 @@
       <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0</v>
       </c>
@@ -4293,21 +6236,33 @@
         <f>($B$4+A9*$B$3)/3600</f>
         <v>31.5</v>
       </c>
+      <c r="D9">
+        <f>B5</f>
+        <v>3.3190570950991809</v>
+      </c>
+      <c r="E9">
+        <f>B5*B2/3600</f>
+        <v>31.531042403442218</v>
+      </c>
+      <c r="F9" t="str">
+        <f>TEXT(D9,"0.00")&amp;" reports, "&amp;TEXT(E9,"0.0")&amp;" hours"</f>
+        <v>3.32 reports, 31.5 hours</v>
+      </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10">
-        <f t="shared" ref="B10:B19" si="1">A10*$B$2/3600</f>
+        <f t="shared" ref="B10:B19" si="2">A10*$B$2/3600</f>
         <v>9.5</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C10:C19" si="2">($B$4+A10*$B$3)/3600</f>
+        <f t="shared" ref="C10:C19" si="3">($B$4+A10*$B$3)/3600</f>
         <v>31.509352777777778</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -4316,120 +6271,120 @@
         <v>19</v>
       </c>
       <c r="C11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.518705555555556</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
       <c r="B12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28.5</v>
       </c>
       <c r="C12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.52805833333333</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
       <c r="B13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="C13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.537411111111108</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
       <c r="B14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>47.5</v>
       </c>
       <c r="C14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.54676388888889</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>6</v>
       </c>
       <c r="B15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>57</v>
       </c>
       <c r="C15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.556116666666668</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>7</v>
       </c>
       <c r="B16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>66.5</v>
       </c>
       <c r="C16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.565469444444446</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>8</v>
       </c>
       <c r="B17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>76</v>
       </c>
       <c r="C17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.574822222222224</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9</v>
       </c>
       <c r="B18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>85.5</v>
       </c>
       <c r="C18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.584174999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>10</v>
       </c>
       <c r="B19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="C19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31.593527777777776</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -4439,8 +6394,11 @@
       <c r="C22" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D22" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>0</v>
       </c>
@@ -4452,143 +6410,155 @@
         <f>($C$4+A23*$C$3)/3600</f>
         <v>19</v>
       </c>
+      <c r="D23">
+        <f>C5</f>
+        <v>3.7081873415278492</v>
+      </c>
+      <c r="E23">
+        <f>C5*C2/3600</f>
+        <v>19.09716480886842</v>
+      </c>
+      <c r="F23" t="str">
+        <f>TEXT(D23,"0.00")&amp;" reports, "&amp;TEXT(E23,"0.0")&amp;" hours"</f>
+        <v>3.71 reports, 19.1 hours</v>
+      </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
-        <f t="shared" ref="B24:B33" si="3">A24*$C$2/3600</f>
+        <f t="shared" ref="B24:B33" si="4">A24*$C$2/3600</f>
         <v>5.15</v>
       </c>
       <c r="C24">
-        <f t="shared" ref="C24:C33" si="4">($C$4+A24*$C$3)/3600</f>
+        <f t="shared" ref="C24:C33" si="5">($C$4+A24*$C$3)/3600</f>
         <v>19.02620277777778</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.3</v>
       </c>
       <c r="C25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.052405555555556</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>3</v>
       </c>
       <c r="B26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>15.45</v>
       </c>
       <c r="C26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.078608333333335</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>4</v>
       </c>
       <c r="B27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20.6</v>
       </c>
       <c r="C27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.104811111111115</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>5</v>
       </c>
       <c r="B28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25.75</v>
       </c>
       <c r="C28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.131013888888887</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>6</v>
       </c>
       <c r="B29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>30.9</v>
       </c>
       <c r="C29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.157216666666667</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>7</v>
       </c>
       <c r="B30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>36.049999999999997</v>
       </c>
       <c r="C30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.183419444444443</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>8</v>
       </c>
       <c r="B31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>41.2</v>
       </c>
       <c r="C31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.209622222222222</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9</v>
       </c>
       <c r="B32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>46.35</v>
       </c>
       <c r="C32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.235825000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>10</v>
       </c>
       <c r="B33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>51.5</v>
       </c>
       <c r="C33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.262027777777778</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>10</v>
       </c>
@@ -4598,8 +6568,11 @@
       <c r="C36" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D36" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0</v>
       </c>
@@ -4611,135 +6584,321 @@
         <f>($D$4+A37*$D$3)/3600</f>
         <v>13</v>
       </c>
+      <c r="D37">
+        <f>D5</f>
+        <v>1.298424938414984</v>
+      </c>
+      <c r="E37">
+        <f>D5*D2/3600</f>
+        <v>13.049170631070588</v>
+      </c>
+      <c r="F37" t="str">
+        <f>TEXT(D37,"0.00")&amp;" reports, "&amp;TEXT(E37,"0.0")&amp;" hours"</f>
+        <v>1.30 reports, 13.0 hours</v>
+      </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1</v>
       </c>
       <c r="B38">
-        <f t="shared" ref="B38:B47" si="5">A38*$D$2/3600</f>
+        <f t="shared" ref="B38:B47" si="6">A38*$D$2/3600</f>
         <v>10.050000000000001</v>
       </c>
       <c r="C38">
-        <f t="shared" ref="C38:C47" si="6">($D$4+A38*$D$3)/3600</f>
+        <f t="shared" ref="C38:C47" si="7">($D$4+A38*$D$3)/3600</f>
         <v>13.037869444444445</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2</v>
       </c>
       <c r="B39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>20.100000000000001</v>
       </c>
       <c r="C39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.075738888888889</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>3</v>
       </c>
       <c r="B40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>30.15</v>
       </c>
       <c r="C40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.113608333333334</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>4</v>
       </c>
       <c r="B41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>40.200000000000003</v>
       </c>
       <c r="C41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.151477777777778</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>5</v>
       </c>
       <c r="B42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>50.25</v>
       </c>
       <c r="C42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.189347222222223</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>6</v>
       </c>
       <c r="B43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>60.3</v>
       </c>
       <c r="C43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.227216666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>7</v>
       </c>
       <c r="B44">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>70.349999999999994</v>
       </c>
       <c r="C44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.26508611111111</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
       <c r="B45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>80.400000000000006</v>
       </c>
       <c r="C45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.302955555555556</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9</v>
       </c>
       <c r="B46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>90.45</v>
       </c>
       <c r="C46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.340825000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>10</v>
       </c>
       <c r="B47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>100.5</v>
       </c>
       <c r="C47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13.378694444444445</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51">
+        <f>A37*$E$2/3600</f>
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <f>($E$4+A37*$E$3)/3600</f>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="D51">
+        <f>E5</f>
+        <v>2.5785152827788682</v>
+      </c>
+      <c r="E51">
+        <f>E5*E2/3600</f>
+        <v>21.229775828212681</v>
+      </c>
+      <c r="F51" t="str">
+        <f>TEXT(D51,"0.00")&amp;" reports, "&amp;TEXT(E51,"0.0")&amp;" hours"</f>
+        <v>2.58 reports, 21.2 hours</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1</v>
+      </c>
+      <c r="B52">
+        <f t="shared" ref="B52:B61" si="8">A38*$E$2/3600</f>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="C52">
+        <f t="shared" ref="C52:C61" si="9">($E$4+A38*$E$3)/3600</f>
+        <v>21.191141666666667</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="8"/>
+        <v>16.466666666666665</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="9"/>
+        <v>21.215616666666666</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>3</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="8"/>
+        <v>24.7</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="9"/>
+        <v>21.240091666666668</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="8"/>
+        <v>32.93333333333333</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="9"/>
+        <v>21.264566666666667</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>5</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="8"/>
+        <v>41.166666666666664</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="9"/>
+        <v>21.289041666666666</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>6</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="8"/>
+        <v>49.4</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="9"/>
+        <v>21.313516666666668</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>7</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="8"/>
+        <v>57.633333333333333</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="9"/>
+        <v>21.337991666666667</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>8</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="8"/>
+        <v>65.86666666666666</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="9"/>
+        <v>21.362466666666666</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>9</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="8"/>
+        <v>74.099999999999994</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="9"/>
+        <v>21.386941666666669</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>10</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="8"/>
+        <v>82.333333333333329</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="9"/>
+        <v>21.411416666666668</v>
       </c>
     </row>
   </sheetData>

--- a/Metrics/Break-Even Graphs.xlsx
+++ b/Metrics/Break-Even Graphs.xlsx
@@ -623,7 +623,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -6162,7 +6161,7 @@
         <v>136.33000000000001</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E5" si="0">AVERAGE(B3,C3,D3)</f>
+        <f t="shared" ref="E3:E4" si="0">AVERAGE(B3,C3,D3)</f>
         <v>88.110000000000014</v>
       </c>
     </row>
